--- a/sen_Vmax/IGD_Vmax.xlsx
+++ b/sen_Vmax/IGD_Vmax.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\代码\MOEA\Platemohjp\PlatEMO-master\PlatEMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\论文\MOPSO_PPHS\1.experiments\sen_Vmax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E1BA8C-E577-4296-9E88-ADF380CA113A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFE3C34-D3D2-4B73-BA8C-B64894FF1FEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4920" yWindow="3150" windowWidth="19200" windowHeight="10050" xr2:uid="{7070C942-013E-4E95-BF91-27ADB266B4E4}"/>
+    <workbookView xWindow="3705" yWindow="2715" windowWidth="19200" windowHeight="10050" xr2:uid="{7070C942-013E-4E95-BF91-27ADB266B4E4}"/>
   </bookViews>
   <sheets>
     <sheet name="myIGD" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="133">
   <si>
     <t>Problem</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Vmax04</t>
   </si>
   <si>
-    <t>Vmax06</t>
-  </si>
-  <si>
     <t>Vmax08</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>1.1442e-1 (2.62e-2) =</t>
   </si>
   <si>
-    <t>1.1394e-1 (2.59e-2) =</t>
-  </si>
-  <si>
     <t>1.0771e-1 (3.39e-2) =</t>
   </si>
   <si>
@@ -101,9 +95,6 @@
     <t>1.9806e-1 (4.00e-2) =</t>
   </si>
   <si>
-    <t>2.0589e-1 (4.10e-2) =</t>
-  </si>
-  <si>
     <t>2.0238e-1 (4.26e-2) =</t>
   </si>
   <si>
@@ -122,9 +113,6 @@
     <t>6.3437e-2 (8.25e-3) =</t>
   </si>
   <si>
-    <t>6.4790e-2 (8.57e-3) =</t>
-  </si>
-  <si>
     <t>6.6920e-2 (1.03e-2) =</t>
   </si>
   <si>
@@ -143,9 +131,6 @@
     <t>4.1345e-2 (1.81e-2) =</t>
   </si>
   <si>
-    <t>4.4396e-2 (1.90e-2) =</t>
-  </si>
-  <si>
     <t>4.5845e-2 (2.31e-2) =</t>
   </si>
   <si>
@@ -164,9 +149,6 @@
     <t>3.6349e-2 (6.04e-3) =</t>
   </si>
   <si>
-    <t>3.9011e-2 (6.89e-3) =</t>
-  </si>
-  <si>
     <t>3.5771e-2 (6.41e-3) =</t>
   </si>
   <si>
@@ -185,9 +167,6 @@
     <t>4.3265e-2 (1.76e-2) =</t>
   </si>
   <si>
-    <t>4.5236e-2 (1.94e-2) =</t>
-  </si>
-  <si>
     <t>4.3317e-2 (1.76e-2) =</t>
   </si>
   <si>
@@ -206,9 +185,6 @@
     <t>5.2243e-2 (5.37e-3) =</t>
   </si>
   <si>
-    <t>4.9441e-2 (7.30e-3) =</t>
-  </si>
-  <si>
     <t>4.9036e-2 (7.81e-3) =</t>
   </si>
   <si>
@@ -227,9 +203,6 @@
     <t>2.9956e-2 (7.05e-3) =</t>
   </si>
   <si>
-    <t>3.2602e-2 (1.30e-2) =</t>
-  </si>
-  <si>
     <t>3.2303e-2 (1.01e-2) =</t>
   </si>
   <si>
@@ -248,9 +221,6 @@
     <t>4.6166e-2 (1.55e-2) =</t>
   </si>
   <si>
-    <t>4.0703e-2 (1.19e-2) =</t>
-  </si>
-  <si>
     <t>4.2852e-2 (1.55e-2) =</t>
   </si>
   <si>
@@ -269,9 +239,6 @@
     <t>9.0376e-2 (1.39e-4) =</t>
   </si>
   <si>
-    <t>9.0448e-2 (1.17e-4) -</t>
-  </si>
-  <si>
     <t>9.0426e-2 (1.36e-4) -</t>
   </si>
   <si>
@@ -290,9 +257,6 @@
     <t>1.0405e-1 (1.49e-2) -</t>
   </si>
   <si>
-    <t>9.5359e-2 (1.82e-2) =</t>
-  </si>
-  <si>
     <t>1.0021e-1 (1.73e-2) -</t>
   </si>
   <si>
@@ -311,9 +275,6 @@
     <t>8.0580e-2 (1.95e-3) +</t>
   </si>
   <si>
-    <t>8.0575e-2 (1.97e-3) +</t>
-  </si>
-  <si>
     <t>8.0970e-2 (1.03e-4) -</t>
   </si>
   <si>
@@ -332,9 +293,6 @@
     <t>3.9032e-1 (5.17e-2) -</t>
   </si>
   <si>
-    <t>3.7552e-1 (4.21e-2) =</t>
-  </si>
-  <si>
     <t>3.8290e-1 (4.77e-2) -</t>
   </si>
   <si>
@@ -353,9 +311,6 @@
     <t>8.2689e-2 (9.01e-5) -</t>
   </si>
   <si>
-    <t>8.2701e-2 (8.83e-5) -</t>
-  </si>
-  <si>
     <t>8.2702e-2 (9.43e-5) -</t>
   </si>
   <si>
@@ -374,9 +329,6 @@
     <t>9.0514e-2 (1.01e-4) -</t>
   </si>
   <si>
-    <t>9.0484e-2 (1.01e-4) -</t>
-  </si>
-  <si>
     <t>9.0516e-2 (9.33e-5) -</t>
   </si>
   <si>
@@ -395,9 +347,6 @@
     <t>6.5248e-2 (7.81e-5) -</t>
   </si>
   <si>
-    <t>6.5239e-2 (1.27e-4) -</t>
-  </si>
-  <si>
     <t>6.5281e-2 (1.20e-4) -</t>
   </si>
   <si>
@@ -416,9 +365,6 @@
     <t>2.9791e-1 (2.86e-2) -</t>
   </si>
   <si>
-    <t>2.9589e-1 (2.40e-2) -</t>
-  </si>
-  <si>
     <t>2.8712e-1 (1.36e-2) -</t>
   </si>
   <si>
@@ -437,9 +383,6 @@
     <t>1.7813e-1 (2.09e-2) -</t>
   </si>
   <si>
-    <t>1.6773e-1 (2.12e-2) -</t>
-  </si>
-  <si>
     <t>1.6754e-1 (2.44e-2) -</t>
   </si>
   <si>
@@ -458,9 +401,6 @@
     <t>1.7831e-1 (2.87e-2) -</t>
   </si>
   <si>
-    <t>1.5404e-1 (3.24e-2) -</t>
-  </si>
-  <si>
     <t>1.6313e-1 (2.89e-2) -</t>
   </si>
   <si>
@@ -479,9 +419,6 @@
     <t>3.2412e-1 (3.51e-2) -</t>
   </si>
   <si>
-    <t>3.2217e-1 (2.64e-2) -</t>
-  </si>
-  <si>
     <t>3.3379e-1 (1.99e-2) -</t>
   </si>
   <si>
@@ -495,9 +432,6 @@
   </si>
   <si>
     <t>0/13/7</t>
-  </si>
-  <si>
-    <t>1/8/11</t>
   </si>
   <si>
     <t>0/11/9</t>
@@ -926,15 +860,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57601AB0-DF11-47A7-AED7-D0867132BB68}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="2" max="3" width="6.625" customWidth="1"/>
-    <col min="4" max="9" width="22.625" customWidth="1"/>
+    <col min="4" max="8" width="22.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -959,13 +893,10 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -974,27 +905,24 @@
         <v>10367</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1003,27 +931,24 @@
         <v>7129</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1032,27 +957,24 @@
         <v>2000</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -1061,27 +983,24 @@
         <v>7130</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -1090,27 +1009,24 @@
         <v>5327</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -1119,27 +1035,24 @@
         <v>11225</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -1148,27 +1061,24 @@
         <v>10509</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -1177,27 +1087,24 @@
         <v>2308</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -1206,27 +1113,24 @@
         <v>12533</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
@@ -1235,27 +1139,24 @@
         <v>24526</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
@@ -1264,27 +1165,24 @@
         <v>22277</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
@@ -1293,27 +1191,24 @@
         <v>22277</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
@@ -1322,27 +1217,24 @@
         <v>22283</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
@@ -1351,27 +1243,24 @@
         <v>22283</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1">
         <v>2</v>
@@ -1380,27 +1269,24 @@
         <v>29148</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="B17" s="1">
         <v>2</v>
@@ -1409,27 +1295,24 @@
         <v>22283</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -1438,27 +1321,24 @@
         <v>22283</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -1467,27 +1347,24 @@
         <v>12625</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B20" s="1">
         <v>2</v>
@@ -1496,27 +1373,24 @@
         <v>12620</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="B21" s="1">
         <v>2</v>
@@ -1525,47 +1399,41 @@
         <v>12646</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>154</v>
+        <v>126</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
